--- a/output/石巻赤十字病院_随意契約_X線関連.xlsx
+++ b/output/石巻赤十字病院_随意契約_X線関連.xlsx
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2025年度（2026年2月16日〜2026年3月25日）</t>
+          <t>2025年度（2026年2月6日〜2026年3月27日）</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
